--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/141.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/141.xlsx
@@ -426,13 +426,13 @@
         <v>-4.416694403041341</v>
       </c>
       <c r="E2">
-        <v>-11.07621023749055</v>
+        <v>-14.97093336473546</v>
       </c>
       <c r="F2">
-        <v>-0.3101524999992818</v>
+        <v>-0.3833047969731034</v>
       </c>
       <c r="G2">
-        <v>-5.421449842145008</v>
+        <v>-9.07033975662079</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.284307276146956</v>
       </c>
       <c r="E3">
-        <v>-11.51243813864944</v>
+        <v>-14.82656108489692</v>
       </c>
       <c r="F3">
-        <v>-0.2554114969200821</v>
+        <v>-0.1644550993578908</v>
       </c>
       <c r="G3">
-        <v>-6.143638730445939</v>
+        <v>-8.853866494353385</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.104891642880358</v>
       </c>
       <c r="E4">
-        <v>-12.18166508445098</v>
+        <v>-14.70778374014973</v>
       </c>
       <c r="F4">
-        <v>-0.1726393692975499</v>
+        <v>0.2437312220455936</v>
       </c>
       <c r="G4">
-        <v>-5.613186708142977</v>
+        <v>-9.178068219014213</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.882974449093943</v>
       </c>
       <c r="E5">
-        <v>-13.44388211613493</v>
+        <v>-17.41578402589256</v>
       </c>
       <c r="F5">
-        <v>0.3776459247495645</v>
+        <v>-0.09271599717324522</v>
       </c>
       <c r="G5">
-        <v>-5.617252058065202</v>
+        <v>-9.604847197209358</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.609862090626098</v>
       </c>
       <c r="E6">
-        <v>-15.02568261548819</v>
+        <v>-18.31991650389399</v>
       </c>
       <c r="F6">
-        <v>0.2030169641979979</v>
+        <v>0.1030968029701131</v>
       </c>
       <c r="G6">
-        <v>-5.387983537288515</v>
+        <v>-8.897645148564708</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.278479465115895</v>
       </c>
       <c r="E7">
-        <v>-14.8919658349897</v>
+        <v>-18.11838582513063</v>
       </c>
       <c r="F7">
-        <v>0.2595870025025789</v>
+        <v>-0.02012450493111894</v>
       </c>
       <c r="G7">
-        <v>-4.881536280690809</v>
+        <v>-7.801321577234122</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.882441547938116</v>
       </c>
       <c r="E8">
-        <v>-16.57683893123155</v>
+        <v>-19.54634953396933</v>
       </c>
       <c r="F8">
-        <v>0.4784184760349299</v>
+        <v>0.1657752225029377</v>
       </c>
       <c r="G8">
-        <v>-4.496380791560921</v>
+        <v>-8.408958968785191</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.415575803878715</v>
       </c>
       <c r="E9">
-        <v>-16.62577362135844</v>
+        <v>-20.05976074611495</v>
       </c>
       <c r="F9">
-        <v>0.6332610528032275</v>
+        <v>0.5346406000303352</v>
       </c>
       <c r="G9">
-        <v>-4.594561640619086</v>
+        <v>-7.597329071649771</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.883647825678112</v>
       </c>
       <c r="E10">
-        <v>-17.9217685406656</v>
+        <v>-20.98744581743026</v>
       </c>
       <c r="F10">
-        <v>0.4688359219193453</v>
+        <v>1.077585730521243</v>
       </c>
       <c r="G10">
-        <v>-4.395064855877066</v>
+        <v>-6.871362850888532</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.29647106823334</v>
       </c>
       <c r="E11">
-        <v>-18.94374096929462</v>
+        <v>-21.74969667629737</v>
       </c>
       <c r="F11">
-        <v>0.6052854288758825</v>
+        <v>0.6622679941470578</v>
       </c>
       <c r="G11">
-        <v>-3.4780735364088</v>
+        <v>-6.657365876684502</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.6764678125077496</v>
       </c>
       <c r="E12">
-        <v>-18.99955441143916</v>
+        <v>-22.05409164214496</v>
       </c>
       <c r="F12">
-        <v>0.5955927018957256</v>
+        <v>1.164829385384087</v>
       </c>
       <c r="G12">
-        <v>-2.74225182157715</v>
+        <v>-5.950670341507361</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.04250307505434281</v>
       </c>
       <c r="E13">
-        <v>-20.4018643150244</v>
+        <v>-23.2308156130381</v>
       </c>
       <c r="F13">
-        <v>0.8141218213260548</v>
+        <v>1.154756437766045</v>
       </c>
       <c r="G13">
-        <v>-2.37132505717505</v>
+        <v>-5.460169982772324</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.5872532043518387</v>
       </c>
       <c r="E14">
-        <v>-22.76915580185214</v>
+        <v>-23.08062877257371</v>
       </c>
       <c r="F14">
-        <v>1.025562600890629</v>
+        <v>1.075990294903451</v>
       </c>
       <c r="G14">
-        <v>-2.454353539299971</v>
+        <v>-5.576668080299277</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.201872266223445</v>
       </c>
       <c r="E15">
-        <v>-22.88604477293812</v>
+        <v>-26.29155232466039</v>
       </c>
       <c r="F15">
-        <v>1.348606007164769</v>
+        <v>1.368897695063745</v>
       </c>
       <c r="G15">
-        <v>-1.955821797086662</v>
+        <v>-4.675067487043084</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.797529753825337</v>
       </c>
       <c r="E16">
-        <v>-25.04015834585477</v>
+        <v>-26.26054586312987</v>
       </c>
       <c r="F16">
-        <v>1.498045143364605</v>
+        <v>1.883623661610885</v>
       </c>
       <c r="G16">
-        <v>-0.5829716674062936</v>
+        <v>-4.132892822985562</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.36617220492428</v>
       </c>
       <c r="E17">
-        <v>-25.04295241431751</v>
+        <v>-26.89529300783701</v>
       </c>
       <c r="F17">
-        <v>1.657987978231939</v>
+        <v>1.849200025820149</v>
       </c>
       <c r="G17">
-        <v>-0.04422010743637916</v>
+        <v>-3.403738546870005</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.900189604918259</v>
       </c>
       <c r="E18">
-        <v>-25.94373382155326</v>
+        <v>-28.60612331709083</v>
       </c>
       <c r="F18">
-        <v>1.48474321961045</v>
+        <v>1.710440202177204</v>
       </c>
       <c r="G18">
-        <v>0.7244157347805265</v>
+        <v>-2.012799596363059</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.380958851241203</v>
       </c>
       <c r="E19">
-        <v>-27.80009117151756</v>
+        <v>-28.07031880097728</v>
       </c>
       <c r="F19">
-        <v>1.94843844067553</v>
+        <v>2.293682093344696</v>
       </c>
       <c r="G19">
-        <v>0.08946965307600918</v>
+        <v>-2.909613140769466</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.790967718427474</v>
       </c>
       <c r="E20">
-        <v>-27.57513469671253</v>
+        <v>-28.58210429095415</v>
       </c>
       <c r="F20">
-        <v>1.500379482705694</v>
+        <v>2.176756377704741</v>
       </c>
       <c r="G20">
-        <v>0.6714536272432661</v>
+        <v>-1.928811056031749</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.108752513067033</v>
       </c>
       <c r="E21">
-        <v>-27.69770690267815</v>
+        <v>-30.24404519482115</v>
       </c>
       <c r="F21">
-        <v>1.825232043387548</v>
+        <v>2.542596557477114</v>
       </c>
       <c r="G21">
-        <v>1.413519030961981</v>
+        <v>-2.732863114427778</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.321046117865244</v>
       </c>
       <c r="E22">
-        <v>-28.73570560082031</v>
+        <v>-31.15783690788094</v>
       </c>
       <c r="F22">
-        <v>1.67169414527866</v>
+        <v>2.512404222379878</v>
       </c>
       <c r="G22">
-        <v>1.239182392318421</v>
+        <v>-1.48269518134172</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.421522750837837</v>
       </c>
       <c r="E23">
-        <v>-28.93705514062336</v>
+        <v>-30.99641718764052</v>
       </c>
       <c r="F23">
-        <v>1.969472345767415</v>
+        <v>2.442707045843133</v>
       </c>
       <c r="G23">
-        <v>1.998518912115514</v>
+        <v>-2.314731281181209</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.414975967765043</v>
       </c>
       <c r="E24">
-        <v>-30.12239226907909</v>
+        <v>-31.79678421223019</v>
       </c>
       <c r="F24">
-        <v>1.99541515608829</v>
+        <v>1.947071634460911</v>
       </c>
       <c r="G24">
-        <v>2.142405152888858</v>
+        <v>-1.484095542104832</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.317021633059156</v>
       </c>
       <c r="E25">
-        <v>-29.3711908867907</v>
+        <v>-31.97698124994341</v>
       </c>
       <c r="F25">
-        <v>1.958744987901161</v>
+        <v>2.608007761071775</v>
       </c>
       <c r="G25">
-        <v>2.046038482786213</v>
+        <v>-0.8140278827741868</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.14805313444567</v>
       </c>
       <c r="E26">
-        <v>-30.35664570102188</v>
+        <v>-31.78590002495275</v>
       </c>
       <c r="F26">
-        <v>2.041059856717348</v>
+        <v>1.821050444738216</v>
       </c>
       <c r="G26">
-        <v>2.015458973639965</v>
+        <v>-1.788374403710326</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.933663389832564</v>
       </c>
       <c r="E27">
-        <v>-29.68133248615402</v>
+        <v>-31.70984430399393</v>
       </c>
       <c r="F27">
-        <v>1.947020275681937</v>
+        <v>2.139961954407192</v>
       </c>
       <c r="G27">
-        <v>1.70473779041505</v>
+        <v>-1.362313813897202</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.694002696408532</v>
       </c>
       <c r="E28">
-        <v>-29.39987424115529</v>
+        <v>-32.25753832861461</v>
       </c>
       <c r="F28">
-        <v>1.57122808993233</v>
+        <v>2.455644487940056</v>
       </c>
       <c r="G28">
-        <v>2.114066883072697</v>
+        <v>-1.196988480211538</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.445807139341533</v>
       </c>
       <c r="E29">
-        <v>-29.00936581357784</v>
+        <v>-31.86994850253512</v>
       </c>
       <c r="F29">
-        <v>1.392984962402349</v>
+        <v>2.057516203541363</v>
       </c>
       <c r="G29">
-        <v>0.9691941614086989</v>
+        <v>-1.451529705635022</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.198336329553799</v>
       </c>
       <c r="E30">
-        <v>-27.98132070130453</v>
+        <v>-30.90332534746484</v>
       </c>
       <c r="F30">
-        <v>1.425304544989975</v>
+        <v>1.906526363563486</v>
       </c>
       <c r="G30">
-        <v>1.436590222825162</v>
+        <v>-1.957864403684392</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.952702285057109</v>
       </c>
       <c r="E31">
-        <v>-28.01522085772595</v>
+        <v>-30.93570620085669</v>
       </c>
       <c r="F31">
-        <v>1.658271279883696</v>
+        <v>2.261919173651752</v>
       </c>
       <c r="G31">
-        <v>0.8089107885793451</v>
+        <v>-2.337590598129876</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.707388435014189</v>
       </c>
       <c r="E32">
-        <v>-28.27176796720849</v>
+        <v>-30.99939465930057</v>
       </c>
       <c r="F32">
-        <v>1.695223092987777</v>
+        <v>1.749279036224861</v>
       </c>
       <c r="G32">
-        <v>-0.01330954373620409</v>
+        <v>-3.149243669084071</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.454926667403038</v>
       </c>
       <c r="E33">
-        <v>-27.83201691327164</v>
+        <v>-29.9739149275526</v>
       </c>
       <c r="F33">
-        <v>1.555921517063401</v>
+        <v>1.938054026914035</v>
       </c>
       <c r="G33">
-        <v>0.8809979176969751</v>
+        <v>-2.801427823091623</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.192768815855986</v>
       </c>
       <c r="E34">
-        <v>-27.2714190019661</v>
+        <v>-29.33630352303561</v>
       </c>
       <c r="F34">
-        <v>1.920611922880689</v>
+        <v>1.67711498156258</v>
       </c>
       <c r="G34">
-        <v>0.2571487846400948</v>
+        <v>-2.8408696626465</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.912420384075934</v>
       </c>
       <c r="E35">
-        <v>-27.19594745415426</v>
+        <v>-28.85979937405251</v>
       </c>
       <c r="F35">
-        <v>1.786116534627356</v>
+        <v>2.16410058052477</v>
       </c>
       <c r="G35">
-        <v>0.1085880535653003</v>
+        <v>-3.500072111517257</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.612073735479957</v>
       </c>
       <c r="E36">
-        <v>-25.92578295058685</v>
+        <v>-28.67863777137566</v>
       </c>
       <c r="F36">
-        <v>2.10024008070815</v>
+        <v>2.22955320248957</v>
       </c>
       <c r="G36">
-        <v>-1.079841515758888</v>
+        <v>-2.574423715463797</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.288536797777892</v>
       </c>
       <c r="E37">
-        <v>-24.59082051244368</v>
+        <v>-28.20429370449421</v>
       </c>
       <c r="F37">
-        <v>2.223956752316257</v>
+        <v>2.191738230551773</v>
       </c>
       <c r="G37">
-        <v>-0.3270764288572486</v>
+        <v>-3.493742348446171</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.9441627169272453</v>
       </c>
       <c r="E38">
-        <v>-24.46302697594723</v>
+        <v>-27.27203487443114</v>
       </c>
       <c r="F38">
-        <v>2.044921705549199</v>
+        <v>2.647012268599992</v>
       </c>
       <c r="G38">
-        <v>-1.471876318519382</v>
+        <v>-3.192141718181948</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.5845458925010213</v>
       </c>
       <c r="E39">
-        <v>-22.75666627053898</v>
+        <v>-26.98851617375891</v>
       </c>
       <c r="F39">
-        <v>2.692640401880995</v>
+        <v>2.646747191031096</v>
       </c>
       <c r="G39">
-        <v>-1.188420788355905</v>
+        <v>-3.190983027243203</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.217194807858417</v>
       </c>
       <c r="E40">
-        <v>-22.64014410584761</v>
+        <v>-26.21551018912359</v>
       </c>
       <c r="F40">
-        <v>2.771234244323806</v>
+        <v>2.576670622223869</v>
       </c>
       <c r="G40">
-        <v>-2.028951748049163</v>
+        <v>-4.0584088588975</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.1451947102935237</v>
       </c>
       <c r="E41">
-        <v>-22.96748484949207</v>
+        <v>-25.32767568907577</v>
       </c>
       <c r="F41">
-        <v>2.598214801635879</v>
+        <v>2.46636024866267</v>
       </c>
       <c r="G41">
-        <v>-1.893706031133317</v>
+        <v>-4.467939894833042</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.4918380046647361</v>
       </c>
       <c r="E42">
-        <v>-21.64206390608306</v>
+        <v>-24.37082724515106</v>
       </c>
       <c r="F42">
-        <v>2.750530029458235</v>
+        <v>3.052087242038561</v>
       </c>
       <c r="G42">
-        <v>-1.706997883809501</v>
+        <v>-4.815682908823627</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.8095661599215626</v>
       </c>
       <c r="E43">
-        <v>-21.10238754469295</v>
+        <v>-24.68633961468747</v>
       </c>
       <c r="F43">
-        <v>3.008766940341759</v>
+        <v>3.003372611814728</v>
       </c>
       <c r="G43">
-        <v>-2.409333430511422</v>
+        <v>-4.178816710706332</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.091698923722999</v>
       </c>
       <c r="E44">
-        <v>-20.18930227357836</v>
+        <v>-23.74342981375837</v>
       </c>
       <c r="F44">
-        <v>3.015494940387296</v>
+        <v>2.962394933133042</v>
       </c>
       <c r="G44">
-        <v>-2.319233623114617</v>
+        <v>-4.986116414276387</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.332381252181285</v>
       </c>
       <c r="E45">
-        <v>-20.22653538686943</v>
+        <v>-23.01477117508016</v>
       </c>
       <c r="F45">
-        <v>3.086433011293435</v>
+        <v>3.007017428387046</v>
       </c>
       <c r="G45">
-        <v>-2.222168427903186</v>
+        <v>-4.411087896287138</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.532215626083026</v>
       </c>
       <c r="E46">
-        <v>-18.67650213267997</v>
+        <v>-22.51586919365512</v>
       </c>
       <c r="F46">
-        <v>3.293929105285877</v>
+        <v>3.188356993268691</v>
       </c>
       <c r="G46">
-        <v>-2.770818519035521</v>
+        <v>-4.760105470310342</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.692554354495716</v>
       </c>
       <c r="E47">
-        <v>-19.15635282395475</v>
+        <v>-20.78081607693428</v>
       </c>
       <c r="F47">
-        <v>3.289822059702797</v>
+        <v>3.232982801992306</v>
       </c>
       <c r="G47">
-        <v>-2.482463381473923</v>
+        <v>-4.324921016990988</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.816808777958297</v>
       </c>
       <c r="E48">
-        <v>-17.36931282562585</v>
+        <v>-21.46286766112554</v>
       </c>
       <c r="F48">
-        <v>3.614538768130592</v>
+        <v>3.376673068416714</v>
       </c>
       <c r="G48">
-        <v>-3.036271302556442</v>
+        <v>-4.942728404438698</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.909564438076364</v>
       </c>
       <c r="E49">
-        <v>-16.58155760114754</v>
+        <v>-20.11556965978547</v>
       </c>
       <c r="F49">
-        <v>3.423157733592211</v>
+        <v>3.629971252844747</v>
       </c>
       <c r="G49">
-        <v>-2.690001481330833</v>
+        <v>-5.443802645626167</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.973735406942122</v>
       </c>
       <c r="E50">
-        <v>-15.66635300419737</v>
+        <v>-19.9483285862082</v>
       </c>
       <c r="F50">
-        <v>3.824332753298401</v>
+        <v>3.243827788029757</v>
       </c>
       <c r="G50">
-        <v>-3.458703534458524</v>
+        <v>-5.12068677990222</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.01417723220763</v>
       </c>
       <c r="E51">
-        <v>-14.9138700637648</v>
+        <v>-19.59276186407394</v>
       </c>
       <c r="F51">
-        <v>3.805838622663499</v>
+        <v>3.491080547152159</v>
       </c>
       <c r="G51">
-        <v>-4.317876176083418</v>
+        <v>-5.573526372582508</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.033680689716515</v>
       </c>
       <c r="E52">
-        <v>-14.45375446221546</v>
+        <v>-18.85703880594377</v>
       </c>
       <c r="F52">
-        <v>3.62211004619218</v>
+        <v>3.735048001155059</v>
       </c>
       <c r="G52">
-        <v>-4.210866102072017</v>
+        <v>-6.095860937223177</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.037233619212611</v>
       </c>
       <c r="E53">
-        <v>-13.72126020605275</v>
+        <v>-17.13086602675197</v>
       </c>
       <c r="F53">
-        <v>3.622133240479458</v>
+        <v>3.407620874585304</v>
       </c>
       <c r="G53">
-        <v>-4.065125955796681</v>
+        <v>-6.356957042814417</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.028703363842725</v>
       </c>
       <c r="E54">
-        <v>-13.0810154939003</v>
+        <v>-17.54421154875009</v>
       </c>
       <c r="F54">
-        <v>3.547348231354719</v>
+        <v>3.838269206483099</v>
       </c>
       <c r="G54">
-        <v>-4.529900065146042</v>
+        <v>-5.991045754904312</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.011505304903305</v>
       </c>
       <c r="E55">
-        <v>-11.80538512220563</v>
+        <v>-15.8126136576971</v>
       </c>
       <c r="F55">
-        <v>4.335032854267935</v>
+        <v>4.014984824522318</v>
       </c>
       <c r="G55">
-        <v>-4.979343038103037</v>
+        <v>-7.478715535523223</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.98882208107067</v>
       </c>
       <c r="E56">
-        <v>-11.88264994572451</v>
+        <v>-15.71226720216113</v>
       </c>
       <c r="F56">
-        <v>3.951507030445792</v>
+        <v>3.983127470945455</v>
       </c>
       <c r="G56">
-        <v>-5.4932555748918</v>
+        <v>-7.083022579941835</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.961255944502807</v>
       </c>
       <c r="E57">
-        <v>-11.36432986775457</v>
+        <v>-16.10751694202461</v>
       </c>
       <c r="F57">
-        <v>4.083232358104164</v>
+        <v>3.955918915233102</v>
       </c>
       <c r="G57">
-        <v>-5.89403352842151</v>
+        <v>-7.421916505705948</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.931180189965814</v>
       </c>
       <c r="E58">
-        <v>-10.6180373512905</v>
+        <v>-15.71326346644282</v>
       </c>
       <c r="F58">
-        <v>4.163855700683834</v>
+        <v>3.612308803082256</v>
       </c>
       <c r="G58">
-        <v>-5.686194168920525</v>
+        <v>-7.903097678747936</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.897185685063982</v>
       </c>
       <c r="E59">
-        <v>-10.39370580589852</v>
+        <v>-14.4348299693374</v>
       </c>
       <c r="F59">
-        <v>3.937469516437952</v>
+        <v>3.977690067313479</v>
       </c>
       <c r="G59">
-        <v>-6.065907121183852</v>
+        <v>-7.544810577214772</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.860352820311506</v>
       </c>
       <c r="E60">
-        <v>-8.794633706680004</v>
+        <v>-14.36430351514194</v>
       </c>
       <c r="F60">
-        <v>3.824881132519054</v>
+        <v>3.698207189282953</v>
       </c>
       <c r="G60">
-        <v>-6.701988720008338</v>
+        <v>-7.998163304453647</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.817898592301834</v>
       </c>
       <c r="E61">
-        <v>-9.686240425576212</v>
+        <v>-14.04565744159222</v>
       </c>
       <c r="F61">
-        <v>4.208973559644712</v>
+        <v>3.775835155334101</v>
       </c>
       <c r="G61">
-        <v>-6.860812142254874</v>
+        <v>-8.361263939200912</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.7691337884114</v>
       </c>
       <c r="E62">
-        <v>-8.210578300014728</v>
+        <v>-12.70363058399709</v>
       </c>
       <c r="F62">
-        <v>3.835948121020455</v>
+        <v>3.662748094238718</v>
       </c>
       <c r="G62">
-        <v>-7.377409531475986</v>
+        <v>-8.694698775370766</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.711807615060479</v>
       </c>
       <c r="E63">
-        <v>-10.15804854701336</v>
+        <v>-12.96948370756539</v>
       </c>
       <c r="F63">
-        <v>3.798434674817277</v>
+        <v>3.654868663503289</v>
       </c>
       <c r="G63">
-        <v>-7.592932667173619</v>
+        <v>-9.267426464210221</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.644856248850798</v>
       </c>
       <c r="E64">
-        <v>-7.84775243404617</v>
+        <v>-12.72318453476221</v>
       </c>
       <c r="F64">
-        <v>3.593468414872984</v>
+        <v>3.354418149773103</v>
       </c>
       <c r="G64">
-        <v>-8.286664106018975</v>
+        <v>-9.396507945331944</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.568554861861954</v>
       </c>
       <c r="E65">
-        <v>-7.949874051393144</v>
+        <v>-12.63689899102006</v>
       </c>
       <c r="F65">
-        <v>3.460964421855981</v>
+        <v>3.456373609709666</v>
       </c>
       <c r="G65">
-        <v>-8.127983037230628</v>
+        <v>-9.062166019684328</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.48365011202236</v>
       </c>
       <c r="E66">
-        <v>-6.884129393005979</v>
+        <v>-12.25647547505769</v>
       </c>
       <c r="F66">
-        <v>3.531340859663021</v>
+        <v>3.106776057971385</v>
       </c>
       <c r="G66">
-        <v>-7.9535901193129</v>
+        <v>-9.213011027181221</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.394322077013577</v>
       </c>
       <c r="E67">
-        <v>-6.737945723564373</v>
+        <v>-11.42798209840639</v>
       </c>
       <c r="F67">
-        <v>3.563431812847474</v>
+        <v>2.937018726115682</v>
       </c>
       <c r="G67">
-        <v>-8.280208542217395</v>
+        <v>-9.111158783120002</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.303723291633148</v>
       </c>
       <c r="E68">
-        <v>-7.152196940364034</v>
+        <v>-11.07957942215226</v>
       </c>
       <c r="F68">
-        <v>3.430584875725712</v>
+        <v>3.189637649273419</v>
       </c>
       <c r="G68">
-        <v>-8.302210427871392</v>
+        <v>-9.714727514203307</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.218509814637282</v>
       </c>
       <c r="E69">
-        <v>-6.128580675670227</v>
+        <v>-11.44821984874666</v>
       </c>
       <c r="F69">
-        <v>2.768999309071053</v>
+        <v>3.102423815637076</v>
       </c>
       <c r="G69">
-        <v>-8.295986602257562</v>
+        <v>-10.36980171278659</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.141947035913721</v>
       </c>
       <c r="E70">
-        <v>-6.779462773266695</v>
+        <v>-10.89503504939168</v>
       </c>
       <c r="F70">
-        <v>3.141232828458233</v>
+        <v>3.437374174959056</v>
       </c>
       <c r="G70">
-        <v>-8.672504878075491</v>
+        <v>-9.569685893036759</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.078560217131335</v>
       </c>
       <c r="E71">
-        <v>-7.354972949479498</v>
+        <v>-11.26630199091053</v>
       </c>
       <c r="F71">
-        <v>2.979858574718862</v>
+        <v>2.857147541137754</v>
       </c>
       <c r="G71">
-        <v>-9.138646242732571</v>
+        <v>-9.392247273222901</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.028218354783802</v>
       </c>
       <c r="E72">
-        <v>-7.3860880943862</v>
+        <v>-12.13429271785674</v>
       </c>
       <c r="F72">
-        <v>3.088825336352719</v>
+        <v>2.642423113188483</v>
       </c>
       <c r="G72">
-        <v>-8.677106536375078</v>
+        <v>-9.243421698504966</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.9885242060318349</v>
       </c>
       <c r="E73">
-        <v>-6.800320924546025</v>
+        <v>-11.4640015806634</v>
       </c>
       <c r="F73">
-        <v>2.818744428343969</v>
+        <v>2.548844104429028</v>
       </c>
       <c r="G73">
-        <v>-8.074471379133849</v>
+        <v>-9.300548472330629</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.953570050323194</v>
       </c>
       <c r="E74">
-        <v>-6.775708668314336</v>
+        <v>-11.70544170085635</v>
       </c>
       <c r="F74">
-        <v>2.829718639696257</v>
+        <v>2.368263324088347</v>
       </c>
       <c r="G74">
-        <v>-8.741344362019097</v>
+        <v>-8.88450890386488</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.9151573945382521</v>
       </c>
       <c r="E75">
-        <v>-7.759972493881488</v>
+        <v>-12.26319573048508</v>
       </c>
       <c r="F75">
-        <v>2.927989521425168</v>
+        <v>3.048230363411127</v>
       </c>
       <c r="G75">
-        <v>-7.959770907834719</v>
+        <v>-9.380193576914415</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.8656455206894992</v>
       </c>
       <c r="E76">
-        <v>-6.71612300732141</v>
+        <v>-12.3783367106041</v>
       </c>
       <c r="F76">
-        <v>2.735808283975682</v>
+        <v>2.336788676251577</v>
       </c>
       <c r="G76">
-        <v>-8.186063248171601</v>
+        <v>-9.008819888864512</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.7969618875835691</v>
       </c>
       <c r="E77">
-        <v>-7.492181183437902</v>
+        <v>-13.12918487191989</v>
       </c>
       <c r="F77">
-        <v>2.465843347403323</v>
+        <v>2.685163557703326</v>
       </c>
       <c r="G77">
-        <v>-7.515210989548149</v>
+        <v>-8.265572620388278</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.70500744322404</v>
       </c>
       <c r="E78">
-        <v>-8.497090322006024</v>
+        <v>-11.83095741492695</v>
       </c>
       <c r="F78">
-        <v>2.504925721467404</v>
+        <v>2.076487473800277</v>
       </c>
       <c r="G78">
-        <v>-7.698290778960924</v>
+        <v>-8.498711168900373</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.5870178659907735</v>
       </c>
       <c r="E79">
-        <v>-9.008296167309906</v>
+        <v>-13.24265484513009</v>
       </c>
       <c r="F79">
-        <v>2.485740732418567</v>
+        <v>2.243940287541392</v>
       </c>
       <c r="G79">
-        <v>-6.488405563996719</v>
+        <v>-7.953384865489466</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.4442868040156568</v>
       </c>
       <c r="E80">
-        <v>-9.573101030968576</v>
+        <v>-13.0868572253702</v>
       </c>
       <c r="F80">
-        <v>1.815995746846334</v>
+        <v>2.243608940580272</v>
       </c>
       <c r="G80">
-        <v>-6.442355875545457</v>
+        <v>-7.239657731586911</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.2793448069768049</v>
       </c>
       <c r="E81">
-        <v>-10.66599389103173</v>
+        <v>-13.85533020752384</v>
       </c>
       <c r="F81">
-        <v>2.306932658319877</v>
+        <v>2.17228816393404</v>
       </c>
       <c r="G81">
-        <v>-6.570963948655064</v>
+        <v>-7.396398820689245</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.09541399338989567</v>
       </c>
       <c r="E82">
-        <v>-10.21891576615046</v>
+        <v>-14.34358574655685</v>
       </c>
       <c r="F82">
-        <v>2.473914959376202</v>
+        <v>2.075287997801023</v>
       </c>
       <c r="G82">
-        <v>-6.392475885905258</v>
+        <v>-6.981590775164105</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.1022962491424805</v>
       </c>
       <c r="E83">
-        <v>-10.95304932990394</v>
+        <v>-14.52744179126827</v>
       </c>
       <c r="F83">
-        <v>2.148331778645078</v>
+        <v>1.996554989634542</v>
       </c>
       <c r="G83">
-        <v>-5.526725190293832</v>
+        <v>-6.279159222641544</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.3128149609804767</v>
       </c>
       <c r="E84">
-        <v>-12.70527442006187</v>
+        <v>-15.56723376511748</v>
       </c>
       <c r="F84">
-        <v>2.377700085541039</v>
+        <v>1.884165413892316</v>
       </c>
       <c r="G84">
-        <v>-5.759380399157193</v>
+        <v>-6.075365349789549</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.5341252003590071</v>
       </c>
       <c r="E85">
-        <v>-13.73706005186552</v>
+        <v>-16.95935460218546</v>
       </c>
       <c r="F85">
-        <v>1.972702978638333</v>
+        <v>1.92468086356324</v>
       </c>
       <c r="G85">
-        <v>-5.397852273541083</v>
+        <v>-5.297152099327532</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.7693391638192045</v>
       </c>
       <c r="E86">
-        <v>-14.76954306866634</v>
+        <v>-17.57233337233773</v>
       </c>
       <c r="F86">
-        <v>1.769978280886015</v>
+        <v>1.501746288920313</v>
       </c>
       <c r="G86">
-        <v>-4.872985141562872</v>
+        <v>-4.983785790216739</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.018177362051683</v>
       </c>
       <c r="E87">
-        <v>-15.14982620193447</v>
+        <v>-19.0839425245721</v>
       </c>
       <c r="F87">
-        <v>1.831787743013303</v>
+        <v>1.465806740782454</v>
       </c>
       <c r="G87">
-        <v>-5.022760842850579</v>
+        <v>-5.651499651668963</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.281384008788729</v>
       </c>
       <c r="E88">
-        <v>-16.09269977507151</v>
+        <v>-19.1767490708853</v>
       </c>
       <c r="F88">
-        <v>1.672544050233932</v>
+        <v>1.001069433524653</v>
       </c>
       <c r="G88">
-        <v>-4.571543417484534</v>
+        <v>-5.442104335764521</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.554612350423624</v>
       </c>
       <c r="E89">
-        <v>-17.92156475933526</v>
+        <v>-21.18899913856366</v>
       </c>
       <c r="F89">
-        <v>1.557586535543028</v>
+        <v>0.9972854512286646</v>
       </c>
       <c r="G89">
-        <v>-4.240177672276724</v>
+        <v>-5.153663124018901</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.831715199462011</v>
       </c>
       <c r="E90">
-        <v>-19.71558766458398</v>
+        <v>-22.70674890155243</v>
       </c>
       <c r="F90">
-        <v>1.407710021354513</v>
+        <v>0.8393306981280493</v>
       </c>
       <c r="G90">
-        <v>-3.597412082008448</v>
+        <v>-4.897731469468924</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.102840342169701</v>
       </c>
       <c r="E91">
-        <v>-21.32578622443935</v>
+        <v>-23.79685675010086</v>
       </c>
       <c r="F91">
-        <v>1.054222456292686</v>
+        <v>0.6217533728435368</v>
       </c>
       <c r="G91">
-        <v>-3.636536109191555</v>
+        <v>-5.120941691908745</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.35531257583744</v>
       </c>
       <c r="E92">
-        <v>-22.95245937273462</v>
+        <v>-25.62971131996536</v>
       </c>
       <c r="F92">
-        <v>1.100357550424202</v>
+        <v>0.4221002614207999</v>
       </c>
       <c r="G92">
-        <v>-3.388119393015724</v>
+        <v>-4.772867623364233</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.575358476551827</v>
       </c>
       <c r="E93">
-        <v>-24.4194404136234</v>
+        <v>-27.47957483820267</v>
       </c>
       <c r="F93">
-        <v>0.4290718014827606</v>
+        <v>-0.2024299462044285</v>
       </c>
       <c r="G93">
-        <v>-3.572334699548469</v>
+        <v>-5.025525148375871</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.746789240846687</v>
       </c>
       <c r="E94">
-        <v>-26.63088446747716</v>
+        <v>-28.86399274098361</v>
       </c>
       <c r="F94">
-        <v>0.3620916700271982</v>
+        <v>-0.3546234040185733</v>
       </c>
       <c r="G94">
-        <v>-3.521799221891494</v>
+        <v>-5.102535058710397</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.85802607614312</v>
       </c>
       <c r="E95">
-        <v>-28.52697011991076</v>
+        <v>-30.95840744105714</v>
       </c>
       <c r="F95">
-        <v>-0.04221292172676776</v>
+        <v>-0.3205509960066241</v>
       </c>
       <c r="G95">
-        <v>-3.574579249424095</v>
+        <v>-4.87494829506766</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.891018879774175</v>
       </c>
       <c r="E96">
-        <v>-31.19696745178122</v>
+        <v>-33.30088062608583</v>
       </c>
       <c r="F96">
-        <v>-0.1596704492393209</v>
+        <v>-0.8569337999325544</v>
       </c>
       <c r="G96">
-        <v>-3.280294924801661</v>
+        <v>-4.016795301468862</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.843707399549198</v>
       </c>
       <c r="E97">
-        <v>-32.83455648667197</v>
+        <v>-35.79223645106471</v>
       </c>
       <c r="F97">
-        <v>-0.5943214524274438</v>
+        <v>-1.312804262510789</v>
       </c>
       <c r="G97">
-        <v>-4.028825823958573</v>
+        <v>-5.069985774968282</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.696562511920022</v>
       </c>
       <c r="E98">
-        <v>-35.49635275211454</v>
+        <v>-37.92833801861585</v>
       </c>
       <c r="F98">
-        <v>-1.003861326167103</v>
+        <v>-1.100763744946589</v>
       </c>
       <c r="G98">
-        <v>-3.945919832018604</v>
+        <v>-5.667718014265852</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.469290876410421</v>
       </c>
       <c r="E99">
-        <v>-38.67046886746688</v>
+        <v>-39.59630405715006</v>
       </c>
       <c r="F99">
-        <v>-0.9123548926494525</v>
+        <v>-2.108485115963229</v>
       </c>
       <c r="G99">
-        <v>-3.991731161191039</v>
+        <v>-5.228302683747309</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.134973613119843</v>
       </c>
       <c r="E100">
-        <v>-40.98560365491127</v>
+        <v>-42.81066698524558</v>
       </c>
       <c r="F100">
-        <v>-1.604100488072638</v>
+        <v>-2.120674542295424</v>
       </c>
       <c r="G100">
-        <v>-4.876669778748081</v>
+        <v>-5.882794226315683</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.754465476650771</v>
       </c>
       <c r="E101">
-        <v>-42.60538899424087</v>
+        <v>-45.08582666838725</v>
       </c>
       <c r="F101">
-        <v>-1.664008018643099</v>
+        <v>-2.540298960796764</v>
       </c>
       <c r="G101">
-        <v>-4.465506643861678</v>
+        <v>-5.228315925929466</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.255619307287249</v>
       </c>
       <c r="E102">
-        <v>-46.03273284762813</v>
+        <v>-46.80841063192798</v>
       </c>
       <c r="F102">
-        <v>-1.696167726321984</v>
+        <v>-2.499790138065062</v>
       </c>
       <c r="G102">
-        <v>-5.055813329514662</v>
+        <v>-5.987079721348265</v>
       </c>
     </row>
   </sheetData>
